--- a/stuff/radar_technical_grammar.xlsx
+++ b/stuff/radar_technical_grammar.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method vocabulary" sheetId="1" r:id="R61c1b886062142d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal grammar" sheetId="2" r:id="R616dd515ee4f43fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query families" sheetId="3" r:id="R867c6b71e53240e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Writing contract" sheetId="4" r:id="R680e51590f1544a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method vocabulary" sheetId="1" r:id="R32d3ba2845174292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal grammar" sheetId="2" r:id="R171db8dbd3854fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query families" sheetId="3" r:id="R7adc1d6145fe4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Writing contract" sheetId="4" r:id="R40855a1f7bb14c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surface terms" sheetId="5" r:id="Rda11b47aa93d470a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,12 +29,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF111111"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -48,7 +54,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -66,6 +72,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1040,4 +1058,243 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>Technical form</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>Surface wording</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>Use on surface pages</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>Glossary / Stuff treatment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="8" t="str">
+        <x:v>HPC</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>high-performance computing</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>Expand in WHAT/WHY. Keep acronym only in an official title.</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>Glossary keeps High-performance computing (HPC).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>R&amp;I</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>research and innovation</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>Expand in WHAT/WHY when space permits.</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>Technical shorthand may remain in scanner notes and Stuff.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>R&amp;D</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>research and development</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>Expand in reader-facing consequence text.</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>Technical shorthand may remain in bibliographic titles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>FP10</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>the next EU research framework programme</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Do not show unexplained programme shorthand.</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Glossary can retain FP10 as an alias.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>MFF</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>the EU long-term budget</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>Prefer the plain description on surface pages.</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>Glossary can retain Multiannual Financial Framework.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>MSCA</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>Marie Skłodowska-Curie Actions</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>Expand on first visible use.</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>Keep acronym as a search/source alias.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>FDI</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>foreign direct investment</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>Expand in WHAT/WHY.</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>Keep acronym in technical query grammar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>TRL</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>technology readiness level</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>Expand unless the source title itself uses TRL.</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>Glossary explains the 1–9 scale.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="8" t="str">
+        <x:v>LLM</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>large language model</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>Expand in reader-facing prose.</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>Keep acronym in technical source/search material.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>GPU</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>graphics processor</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>Use plain wording unless hardware specificity is essential.</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>Technical term can remain in Stuff/search grammar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="8" t="str">
+        <x:v>SME</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>small and medium-sized firm</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>Prefer plain wording on cards and matrices.</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>Keep SME as source/search shorthand.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="8" t="str">
+        <x:v>IP</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>intellectual property</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>Expand in reader-facing consequence text.</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>Keep IP as a query/search alias.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="8" t="str">
+        <x:v>JRC</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>Joint Research Centre</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Expand in WHAT/WHY; official titles may retain JRC.</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>Glossary/source lists retain the acronym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="8" t="str">
+        <x:v>ERC</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>European Research Council</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>Expand in WHAT/WHY; official titles may retain ERC.</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>Glossary/source lists retain the acronym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="8" t="str">
+        <x:v>EIC</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>European Innovation Council</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>Expand in WHAT/WHY; official titles may retain EIC.</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>Glossary/source lists retain the acronym.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>